--- a/JsonConverter/ExcelFiles/EpisodeCondition.xlsx
+++ b/JsonConverter/ExcelFiles/EpisodeCondition.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="15900" windowHeight="6312"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17868" windowHeight="6312"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="HeroBasic" sheetId="1" r:id="rId4"/>
@@ -19,12 +19,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <x:si>
-    <x:t>int</x:t>
+    <x:t>episode_test_02</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
+    <x:t>episodeCondition_test_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_affinity_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Affinity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건 대상 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 에피소드 ID</x:t>
   </x:si>
   <x:si>
     <x:t>조건 타입</x:t>
@@ -39,22 +60,13 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>episode_test_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>Day</x:t>
   </x:si>
   <x:si>
-    <x:t>EpisodeId</x:t>
+    <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>연결 에피소드 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조건 대상 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetId</x:t>
+    <x:t>ID</x:t>
   </x:si>
   <x:si>
     <x:t>episodeCondition_test_01</x:t>
@@ -63,7 +75,13 @@
     <x:t>ConditionType</x:t>
   </x:si>
   <x:si>
+    <x:t>episode_test_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>RequiredValue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episodeCondition_affinity_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -140,13 +158,13 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffffc000"/>
+        <x:bgColor rgb="ffd86dcd"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffd86dcd"/>
+        <x:bgColor rgb="ffffc000"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -309,7 +327,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -328,16 +346,13 @@
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1022,8 +1037,8 @@
   <x:dimension ref="A1:L35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="24.7734375" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
+    <x:col min="1" max="1" width="27.47265625" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="32.42578125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="3" max="3" width="32.76171875" style="2" bestFit="1" customWidth="1"/>
     <x:col min="4" max="4" width="20.28515625" style="2" customWidth="1"/>
     <x:col min="5" max="5" width="30.5703125" style="2" customWidth="1"/>
@@ -1031,68 +1046,68 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A1" s="13" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B1" s="14" t="s">
+      <x:c r="A1" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="14" t="s">
+      <x:c r="D1" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E1" s="15" t="s">
-        <x:v>3</x:v>
-      </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="16.399999999999999">
-      <x:c r="A2" s="16" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="17" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="17" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="17" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E2" s="18" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="20" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="20" t="s">
+      <x:c r="A2" s="15" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E2" s="17" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="19" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C3" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D3" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A4" s="21" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D3" s="20" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E3" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A4" s="22" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B4" s="23" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="23" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="23"/>
-      <x:c r="E4" s="24">
+      <x:c r="D4" s="22"/>
+      <x:c r="E4" s="23">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
@@ -1104,11 +1119,19 @@
       <x:c r="L4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="5"/>
-      <x:c r="C5" s="5"/>
-      <x:c r="D5" s="12"/>
-      <x:c r="E5" s="12"/>
+      <x:c r="A5" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D5" s="22"/>
+      <x:c r="E5" s="23">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="4"/>
@@ -1118,11 +1141,21 @@
       <x:c r="L5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="5"/>
-      <x:c r="C6" s="5"/>
-      <x:c r="D6" s="12"/>
-      <x:c r="E6" s="12"/>
+      <x:c r="A6" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B6" s="22" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="22" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="23">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
@@ -1135,8 +1168,8 @@
       <x:c r="A7" s="3"/>
       <x:c r="B7" s="3"/>
       <x:c r="C7" s="3"/>
-      <x:c r="D7" s="12"/>
-      <x:c r="E7" s="12"/>
+      <x:c r="D7" s="11"/>
+      <x:c r="E7" s="11"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
@@ -1147,10 +1180,10 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="3"/>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6"/>
-      <x:c r="D8" s="12"/>
-      <x:c r="E8" s="12"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="5"/>
+      <x:c r="D8" s="11"/>
+      <x:c r="E8" s="11"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
@@ -1161,10 +1194,10 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="3"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
-      <x:c r="D9" s="12"/>
-      <x:c r="E9" s="12"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="5"/>
+      <x:c r="D9" s="11"/>
+      <x:c r="E9" s="11"/>
       <x:c r="F9" s="4"/>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
@@ -1177,8 +1210,8 @@
       <x:c r="A10" s="3"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="12"/>
-      <x:c r="E10" s="12"/>
+      <x:c r="D10" s="11"/>
+      <x:c r="E10" s="11"/>
       <x:c r="F10" s="4"/>
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
@@ -1202,9 +1235,9 @@
       <x:c r="L11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="5"/>
       <x:c r="D12" s="4"/>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="4"/>
@@ -1258,110 +1291,110 @@
       <x:c r="L15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="7"/>
-      <x:c r="B16" s="7"/>
-      <x:c r="C16" s="7"/>
+      <x:c r="A16" s="6"/>
+      <x:c r="B16" s="6"/>
+      <x:c r="C16" s="6"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="8"/>
-      <x:c r="B17" s="8"/>
-      <x:c r="C17" s="8"/>
+      <x:c r="A17" s="7"/>
+      <x:c r="B17" s="7"/>
+      <x:c r="C17" s="7"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="8"/>
-      <x:c r="B18" s="8"/>
-      <x:c r="C18" s="8"/>
+      <x:c r="A18" s="7"/>
+      <x:c r="B18" s="7"/>
+      <x:c r="C18" s="7"/>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="8"/>
-      <x:c r="B19" s="8"/>
-      <x:c r="C19" s="8"/>
+      <x:c r="A19" s="7"/>
+      <x:c r="B19" s="7"/>
+      <x:c r="C19" s="7"/>
       <x:c r="D19" s="4"/>
       <x:c r="E19" s="4"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="8"/>
-      <x:c r="B20" s="8"/>
-      <x:c r="C20" s="8"/>
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="7"/>
+      <x:c r="C20" s="7"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="8"/>
-      <x:c r="B21" s="8"/>
-      <x:c r="C21" s="8"/>
+      <x:c r="A21" s="7"/>
+      <x:c r="B21" s="7"/>
+      <x:c r="C21" s="7"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="8"/>
-      <x:c r="B22" s="8"/>
-      <x:c r="C22" s="8"/>
+      <x:c r="A22" s="7"/>
+      <x:c r="B22" s="7"/>
+      <x:c r="C22" s="7"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="8"/>
-      <x:c r="B23" s="8"/>
-      <x:c r="C23" s="8"/>
+      <x:c r="A23" s="7"/>
+      <x:c r="B23" s="7"/>
+      <x:c r="C23" s="7"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="8"/>
-      <x:c r="B24" s="8"/>
-      <x:c r="C24" s="8"/>
+      <x:c r="A24" s="7"/>
+      <x:c r="B24" s="7"/>
+      <x:c r="C24" s="7"/>
     </x:row>
     <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="8"/>
-      <x:c r="B25" s="8"/>
-      <x:c r="C25" s="8"/>
+      <x:c r="A25" s="7"/>
+      <x:c r="B25" s="7"/>
+      <x:c r="C25" s="7"/>
       <x:c r="E25" s="4"/>
     </x:row>
     <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="9"/>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
+      <x:c r="A26" s="8"/>
+      <x:c r="B26" s="8"/>
+      <x:c r="C26" s="8"/>
       <x:c r="E26" s="4"/>
     </x:row>
     <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="9"/>
-      <x:c r="B27" s="9"/>
-      <x:c r="C27" s="9"/>
+      <x:c r="A27" s="8"/>
+      <x:c r="B27" s="8"/>
+      <x:c r="C27" s="8"/>
       <x:c r="E27" s="4"/>
     </x:row>
     <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="9"/>
-      <x:c r="B28" s="9"/>
-      <x:c r="C28" s="9"/>
+      <x:c r="A28" s="8"/>
+      <x:c r="B28" s="8"/>
+      <x:c r="C28" s="8"/>
       <x:c r="E28" s="4"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="9"/>
-      <x:c r="B29" s="9"/>
-      <x:c r="C29" s="9"/>
+      <x:c r="A29" s="8"/>
+      <x:c r="B29" s="8"/>
+      <x:c r="C29" s="8"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="9"/>
-      <x:c r="B30" s="9"/>
-      <x:c r="C30" s="9"/>
+      <x:c r="A30" s="8"/>
+      <x:c r="B30" s="8"/>
+      <x:c r="C30" s="8"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="9"/>
-      <x:c r="B31" s="9"/>
-      <x:c r="C31" s="9"/>
+      <x:c r="A31" s="8"/>
+      <x:c r="B31" s="8"/>
+      <x:c r="C31" s="8"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="10"/>
-      <x:c r="B32" s="10"/>
-      <x:c r="C32" s="10"/>
+      <x:c r="A32" s="9"/>
+      <x:c r="B32" s="9"/>
+      <x:c r="C32" s="9"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="10"/>
-      <x:c r="B33" s="10"/>
-      <x:c r="C33" s="10"/>
+      <x:c r="A33" s="9"/>
+      <x:c r="B33" s="9"/>
+      <x:c r="C33" s="9"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="10"/>
-      <x:c r="B34" s="10"/>
-      <x:c r="C34" s="10"/>
+      <x:c r="A34" s="9"/>
+      <x:c r="B34" s="9"/>
+      <x:c r="C34" s="9"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="10"/>
-      <x:c r="B35" s="10"/>
-      <x:c r="C35" s="10"/>
+      <x:c r="A35" s="9"/>
+      <x:c r="B35" s="9"/>
+      <x:c r="C35" s="9"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/EpisodeCondition.xlsx
+++ b/JsonConverter/ExcelFiles/EpisodeCondition.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17868" windowHeight="6312"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="15972" windowHeight="6312"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="HeroBasic" sheetId="1" r:id="rId4"/>
@@ -19,21 +19,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <x:si>
-    <x:t>episode_test_02</x:t>
+    <x:t>episode_affinity_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Affinity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Day</x:t>
   </x:si>
   <x:si>
     <x:t>episodeCondition_test_02</x:t>
   </x:si>
   <x:si>
+    <x:t>episodeCondition_room_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episodeCondition_test_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episodeCondition_affinity_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
     <x:t>hero_01</x:t>
   </x:si>
   <x:si>
-    <x:t>episode_affinity_01</x:t>
+    <x:t>연결 에피소드 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Affinity</x:t>
+    <x:t>EpisodeId</x:t>
   </x:si>
   <x:si>
     <x:t>조건 대상 ID</x:t>
@@ -42,53 +69,38 @@
     <x:t>TargetId</x:t>
   </x:si>
   <x:si>
-    <x:t>EpisodeId</x:t>
+    <x:t>RoomPlaced</x:t>
   </x:si>
   <x:si>
-    <x:t>연결 에피소드 ID</x:t>
+    <x:t>조건 요구값</x:t>
   </x:si>
   <x:si>
     <x:t>조건 타입</x:t>
   </x:si>
   <x:si>
-    <x:t>조건 요구값</x:t>
-  </x:si>
-  <x:si>
     <x:t>조건 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Day</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episodeCondition_test_01</x:t>
   </x:si>
   <x:si>
     <x:t>ConditionType</x:t>
   </x:si>
   <x:si>
-    <x:t>episode_test_01</x:t>
+    <x:t>episode_test_02</x:t>
   </x:si>
   <x:si>
     <x:t>RequiredValue</x:t>
   </x:si>
   <x:si>
-    <x:t>episodeCondition_affinity_01</x:t>
+    <x:t>episode_room_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_01</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -124,19 +136,40 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-      <x:b val="1"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
+    <x:font>
+      <x:name val="나눔고딕"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -179,8 +212,14 @@
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffffff"/>
+        <x:bgColor rgb="ffffffcc"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="11">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -321,13 +360,30 @@
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -430,9 +486,13 @@
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle name="Normal" xfId="1" builtinId="0"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1047,64 +1107,64 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="13" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1" s="13" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D1" s="13" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E1" s="14" t="s">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="16.399999999999999">
       <x:c r="A2" s="15" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="17" t="s">
-        <x:v>14</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" s="10" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="18" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="19" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D3" s="19" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E3" s="20" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A4" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B4" s="22" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="22"/>
       <x:c r="E4" s="23">
@@ -1120,13 +1180,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A5" s="21" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="22" t="s">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="22"/>
       <x:c r="E5" s="23">
@@ -1142,16 +1202,16 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A6" s="21" t="s">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="22" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E6" s="23">
         <x:v>30</x:v>
@@ -1165,11 +1225,21 @@
       <x:c r="L6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3"/>
-      <x:c r="D7" s="11"/>
-      <x:c r="E7" s="11"/>
+      <x:c r="A7" s="21" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="22" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D7" s="24" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E7" s="23">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>

--- a/JsonConverter/ExcelFiles/EpisodeCondition.xlsx
+++ b/JsonConverter/ExcelFiles/EpisodeCondition.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="15972" windowHeight="6312"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="HeroBasic" sheetId="1" r:id="rId4"/>
@@ -19,17 +19,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+  <x:si>
+    <x:t>Affinity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 에피소드 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoomPlaced</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건 대상 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episodeCondition_affinity_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건 요구값</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건 타입</x:t>
+  </x:si>
   <x:si>
     <x:t>episode_affinity_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Affinity</x:t>
-  </x:si>
-  <x:si>
     <x:t>Day</x:t>
   </x:si>
   <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredValue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_room_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>episodeCondition_test_02</x:t>
   </x:si>
   <x:si>
@@ -39,68 +96,23 @@
     <x:t>episodeCondition_test_01</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episodeCondition_affinity_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결 에피소드 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조건 대상 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoomPlaced</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조건 요구값</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조건 타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조건 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredValue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_room_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_01</x:t>
+    <x:t>episode_admitted_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episodeCondition_admitted_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HeroAdmitted</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="10">
+  <x:fonts count="9">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -136,36 +148,15 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
+      <x:b val="1"/>
     </x:font>
     <x:font>
-      <x:name val="나눔고딕"/>
-      <x:sz val="10"/>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
@@ -219,7 +210,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="10">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -360,26 +351,9 @@
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -486,13 +460,12 @@
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="2">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
-    <x:cellStyle name="Normal" xfId="1" builtinId="0"/>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1107,64 +1080,64 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="D1" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E1" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="16.399999999999999">
       <x:c r="A2" s="15" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="17" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" s="10" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="18" t="s">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="20" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A4" s="21" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="22" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="22"/>
       <x:c r="E4" s="23">
@@ -1180,13 +1153,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A5" s="21" t="s">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="22" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="22"/>
       <x:c r="E5" s="23">
@@ -1202,16 +1175,16 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A6" s="21" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C6" s="22" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="D6" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="23">
         <x:v>30</x:v>
@@ -1226,16 +1199,16 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B7" s="22" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="22" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="22" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="D7" s="24" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="23">
         <x:v>0</x:v>
@@ -1249,11 +1222,21 @@
       <x:c r="L7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A8" s="3"/>
-      <x:c r="B8" s="5"/>
-      <x:c r="C8" s="5"/>
-      <x:c r="D8" s="11"/>
-      <x:c r="E8" s="11"/>
+      <x:c r="A8" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
